--- a/02-cascade-civic-rev5-ato/artifacts/customer_responsibility_matrix.xlsx
+++ b/02-cascade-civic-rev5-ato/artifacts/customer_responsibility_matrix.xlsx
@@ -1588,7 +1588,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="23.85" customHeight="1" s="17">
+    <row r="5" ht="45" customHeight="1" s="17">
       <c r="A5" s="21" t="inlineStr">
         <is>
           <t>CSP</t>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>No agency action required. Cascade Civic Systems implements and evidences the control in full.</t>
+          <t>Cascade implements the CSP control. Agency duties and go-live actions remain as listed in the detail rows.</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="23.85" customHeight="1" s="17">
+    <row r="8" ht="45" customHeight="1" s="17">
       <c r="A8" s="21" t="inlineStr">
         <is>
           <t>Inherited</t>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t>Control is satisfied by the underlying IaaS provider's authorization; no action by either party.</t>
+          <t>Underlying IaaS control is inherited. Cascade verifies inheritance; agency retains the listed deletion and facility duties.</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="B4" s="30" t="inlineStr">
         <is>
-          <t>Cascade Civic Systems implements and evidences the control in full. No agency action.</t>
+          <t>Cascade implements and evidences the CSP control. Agency duties are listed in the detail rows.</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>Satisfied by the underlying IaaS provider under its own FedRAMP authorization; documented for traceability, no action by either party.</t>
+          <t>Underlying IaaS control is inherited. Cascade verifies inheritance; agency retains duties listed in the detail rows.</t>
         </is>
       </c>
     </row>
